--- a/output/pdf_financials_xlsx/JWEL.xlsx
+++ b/output/pdf_financials_xlsx/JWEL.xlsx
@@ -1774,25 +1774,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>17.668</v>
+        <v>1.787</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>6.34</v>
+        <v>1.507</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>17.732</v>
+        <v>2.163</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.091</v>
+        <v>1.893</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.953</v>
+        <v>5.029</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>37.118</v>
+        <v>4.298</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>45.905</v>
+        <v>5.335</v>
       </c>
     </row>
     <row r="49">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">

--- a/output/pdf_financials_xlsx/JWEL.xlsx
+++ b/output/pdf_financials_xlsx/JWEL.xlsx
@@ -1382,25 +1382,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>15.881</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>4.833</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>12.445</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>6.775</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>26.24</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>36.863</v>
       </c>
     </row>
     <row r="35">
@@ -1438,25 +1438,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>15.881</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>4.833</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>12.445</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>6.775</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>26.24</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>36.863</v>
       </c>
     </row>
     <row r="37">
@@ -1780,19 +1780,19 @@
         <v>1.507</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.163</v>
+        <v>5.287</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>1.893</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>5.029</v>
+        <v>7.178</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>4.298</v>
+        <v>10.878</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>5.335</v>
+        <v>9.042</v>
       </c>
     </row>
     <row r="49">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -12953,7 +12953,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">

--- a/output/pdf_financials_xlsx/JWEL.xlsx
+++ b/output/pdf_financials_xlsx/JWEL.xlsx
@@ -1227,16 +1227,16 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>3.23</v>
+        <v>7.546</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>3.396</v>
+        <v>8.502000000000001</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>3.495</v>
+        <v>9.045999999999999</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>3.653</v>
+        <v>10.916</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>4.268</v>
@@ -1255,16 +1255,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-18.23</v>
+        <v>-13.914</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-12.235</v>
+        <v>-7.129</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>40.746</v>
+        <v>46.297</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>40.904</v>
+        <v>48.167</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>74.733</v>
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-7.341008573234917</v>
+        <v>-5.603005665825048</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-4.069935699340361</v>
+        <v>-2.371440261593579</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>12.79145401781247</v>
+        <v>15.06273141198839</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>16.56933432661097</v>
@@ -3225,22 +3225,22 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>7.546</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>8.502000000000001</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>9.045999999999999</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>10.916</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>4.268</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>5.095</v>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -14967,7 +14967,11 @@
           <t>Depreciation of property, plant and equipment 6</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -15018,7 +15022,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -15963,7 +15967,11 @@
           <t>Depreciation of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -16014,7 +16022,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -16875,7 +16883,11 @@
           <t>Depreciation of property, plant and equipment 8</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E246" s="5" t="n">
         <v>4.316</v>
       </c>
@@ -16926,7 +16938,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E247" s="5" t="n">

--- a/output/pdf_financials_xlsx/JWEL.xlsx
+++ b/output/pdf_financials_xlsx/JWEL.xlsx
@@ -709,24 +709,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>35.975</v>
+        <v>31.041</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>95.43899999999999</v>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>44.935</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>50.09</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>50.224</v>
+        <v>47.157</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>81.702</v>
+        <v>76.03</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>88.099</v>
+        <v>83.18899999999999</v>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
@@ -3618,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
-        <v>0</v>
+        <v>-82.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>0</v>
@@ -3630,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0</v>
+        <v>-241.96</v>
       </c>
       <c r="H113" s="1" t="inlineStr">
         <is>
@@ -3708,19 +3706,19 @@
         <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.272</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.602</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.471</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.786</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.637</v>
       </c>
       <c r="H116" s="1" t="inlineStr">
         <is>
@@ -14156,7 +14154,11 @@
           <t>Acquisition of business 4</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -14250,7 +14252,11 @@
           <t>Acquisition of intangible assets 9</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -15524,7 +15530,11 @@
           <t>Acquisition of intangible assets 8</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -15918,7 +15928,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -17546,7 +17560,11 @@
           <t>Acquisition of intangible assets 10</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -18619,7 +18637,11 @@
           <t>Income tax recovery (expense) 15</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -19660,7 +19682,11 @@
           <t>Earnings from operations</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E301" s="5" t="n">
         <v>31.041</v>
       </c>
@@ -22235,7 +22261,11 @@
           <t>Earnings from operations 55,449</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E352" t="inlineStr">
         <is>
           <t>-</t>
